--- a/assets/01_엠엔엘뉴스.xlsx
+++ b/assets/01_엠엔엘뉴스.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\공유 드라이브\00_RyanKim_김장길\07_방송_Broadcast\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CEB4B03-1834-4954-8840-F79B5A9D2942}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3608D8A-1E26-4A2A-89C4-947F010E7113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{13C56ADD-2978-4209-B5B1-7D56087C6640}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="828" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="828" uniqueCount="428">
   <si>
     <t>2026년 9월 1주차</t>
   </si>
@@ -65,9 +65,6 @@
     <t>시설·공간·보육</t>
   </si>
   <si>
-    <t>한국전파진흥협...</t>
-  </si>
-  <si>
     <t>서울 강서,독립,유료</t>
   </si>
   <si>
@@ -83,9 +80,6 @@
     <t>행사·네트워크</t>
   </si>
   <si>
-    <t>광운대학교산학...</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
@@ -104,9 +98,6 @@
     <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?pbancClssCd=PBC010&amp;schM=view&amp;pbancSn=178976</t>
   </si>
   <si>
-    <t>구로구 청년창...</t>
-  </si>
-  <si>
     <t>2026.9.2.</t>
   </si>
   <si>
@@ -140,9 +131,6 @@
     <t>2026 예비오션스타 기업 모집 공고</t>
   </si>
   <si>
-    <t>해양수산과학기...</t>
-  </si>
-  <si>
     <t>2026.9.11.</t>
   </si>
   <si>
@@ -152,9 +140,6 @@
     <t>모두의 창업 멘토가 알려주는 사업계획서 작성 방법 특강</t>
   </si>
   <si>
-    <t>(재)경기도경...</t>
-  </si>
-  <si>
     <t>2026.8.31.</t>
   </si>
   <si>
@@ -173,21 +158,12 @@
     <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?pbancClssCd=PBC010&amp;schM=view&amp;pbancSn=178970</t>
   </si>
   <si>
-    <t>벤처박스주식회...</t>
-  </si>
-  <si>
     <t>2026.9.1.</t>
   </si>
   <si>
     <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?pbancClssCd=PBC010&amp;schM=view&amp;pbancSn=178972</t>
   </si>
   <si>
-    <t>주식회사 유디...</t>
-  </si>
-  <si>
-    <t>차세대융합기술...</t>
-  </si>
-  <si>
     <t>2026.9.4.</t>
   </si>
   <si>
@@ -215,9 +191,6 @@
     <t>2026.9.8.</t>
   </si>
   <si>
-    <t>강동구 청년해...</t>
-  </si>
-  <si>
     <t>2026.9.30.</t>
   </si>
   <si>
@@ -230,9 +203,6 @@
     <t>2026.9.7.</t>
   </si>
   <si>
-    <t>부산창조경제혁...</t>
-  </si>
-  <si>
     <t>2026.8.28.</t>
   </si>
   <si>
@@ -266,24 +236,15 @@
     <t>포켓컴퍼니</t>
   </si>
   <si>
-    <t>신한금융희망재...</t>
-  </si>
-  <si>
     <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?pbancClssCd=PBC020&amp;schM=view&amp;pbancSn=178942</t>
   </si>
   <si>
     <t>2026 현대모비스 CSV 오픈 이노베이션 참여 기업 모집</t>
   </si>
   <si>
-    <t>(주)엠와이소...</t>
-  </si>
-  <si>
     <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?pbancClssCd=PBC020&amp;schM=view&amp;pbancSn=178951</t>
   </si>
   <si>
-    <t>중앙대학교 산...</t>
-  </si>
-  <si>
     <t>경북</t>
   </si>
   <si>
@@ -296,9 +257,6 @@
     <t>26년 AI·스마트전자제품 금형지원 기업모집</t>
   </si>
   <si>
-    <t>한국전자정보통...</t>
-  </si>
-  <si>
     <t>전자기기 기반 제품을 개발, 제조하는 창업기업 및 중소기업</t>
   </si>
   <si>
@@ -320,9 +278,6 @@
     <t>싱가포르 현지 진출 지원 국내 블록체인 기업 모집</t>
   </si>
   <si>
-    <t>한국인터넷진흥...</t>
-  </si>
-  <si>
     <t>블록체인 기술 보유 및 해외 진출 역량이 있는 블록체인 중소기업 또는 스타트업</t>
   </si>
   <si>
@@ -338,9 +293,6 @@
     <t>2026년 한전KPS 창업벤처기업 육성 지원사업 참여기업 모집안내</t>
   </si>
   <si>
-    <t>에너지밸리기업...</t>
-  </si>
-  <si>
     <t>에너지, 탄소중립/친환경 분야 창업 7년 미만 또는 벤처기업</t>
   </si>
   <si>
@@ -414,9 +366,6 @@
   </si>
   <si>
     <t>[코레일유통/본사] 제11차 청년창업 제휴사업자 모집공고</t>
-  </si>
-  <si>
-    <t>코레일유통(주...</t>
   </si>
   <si>
     <t>만 18세 이상 39세 이하 예비창업자 또는 창업 3년 이하 소기업 대표자</t>
@@ -432,9 +381,6 @@
     <t>2026년 세종 스타트업 원스톱 지원센터 아카데미 3차</t>
   </si>
   <si>
-    <t>세종창조경제혁...</t>
-  </si>
-  <si>
     <t>세종시 소재 예비창업기업 또는 사업 거점 보유 기업</t>
   </si>
   <si>
@@ -444,9 +390,6 @@
     <t>[인천대학교] 모두의창업 프로젝트(2차) 모집홍보 교육 『AI와 함께하는 BM 스쿨』</t>
   </si>
   <si>
-    <t>국립대학법인 ...</t>
-  </si>
-  <si>
     <t>예비창업자 또는 업력 7년 이내 기창업자</t>
   </si>
   <si>
@@ -456,9 +399,6 @@
     <t>2026년 민간 산림복지 창업 아카데미[1차] 참가자 모집</t>
   </si>
   <si>
-    <t>한국산림복지진...</t>
-  </si>
-  <si>
     <t>산림복지전문업 창업에 관심이 있는 예비창업자</t>
   </si>
   <si>
@@ -495,9 +435,6 @@
     <t>코리아 핀테크 위크 2026 「핀테크 스타트업 1:1 투자 밋업」 참여기업 모집</t>
   </si>
   <si>
-    <t>한국성장금융투...</t>
-  </si>
-  <si>
     <t>핀테크 스타트업 또는 핀테크 영역 사업 확장 희망 스타트업</t>
   </si>
   <si>
@@ -510,9 +447,6 @@
     <t>2026년 대구 콘텐츠 스케일업 액셀러레이팅 프로그램 지원사업 참여기업 추가 모집 공고</t>
   </si>
   <si>
-    <t>대구디지털혁신...</t>
-  </si>
-  <si>
     <t>본점 소재지가 대구인 업력 7년 미만 콘텐츠 기업</t>
   </si>
   <si>
@@ -540,9 +474,6 @@
     <t>[숭실대학교 캠퍼스타운] 2026 석·박사급 실험실 창업스쿨(유형2) 참여자 모집</t>
   </si>
   <si>
-    <t>숭실대학교산학...</t>
-  </si>
-  <si>
     <t>이공계 석·박사급 연구인력 및 예비창업자, 초기창업자</t>
   </si>
   <si>
@@ -555,9 +486,6 @@
     <t>2026년 대전 스타트업스쿨 스타트업 리딩클래스 (4회차 ㅣ 스타트업 IR &amp; 투자유치 마스터클래스)</t>
   </si>
   <si>
-    <t>대전창조경제혁...</t>
-  </si>
-  <si>
     <t>스타트업 역량 강화에 관심이 있는 누구나</t>
   </si>
   <si>
@@ -597,9 +525,6 @@
     <t>2026년 9월 동네창업학교 교육생 모집 공고</t>
   </si>
   <si>
-    <t>충남신용보증재...</t>
-  </si>
-  <si>
     <t>충남 내 창업 예정 청년 예비창업자 또는 충남 소재 청년 기창업자</t>
   </si>
   <si>
@@ -609,9 +534,6 @@
     <t>KAC 한국공항공사 항공산업분야 창업 인큐베이팅 프로그램</t>
   </si>
   <si>
-    <t>(사) 타이드...</t>
-  </si>
-  <si>
     <t>항공산업과 연계된 아이디어를 가진 예비창업자</t>
   </si>
   <si>
@@ -621,9 +543,6 @@
     <t>[서울여자대학교 창업보육센터] 신규 입주기업 모집 공고</t>
   </si>
   <si>
-    <t>서울여자대학교...</t>
-  </si>
-  <si>
     <t>예비창업자 또는 창업 7년 이내 기업</t>
   </si>
   <si>
@@ -643,9 +562,6 @@
   </si>
   <si>
     <t>2026년 충북 바이오 오픈이노베이션 사업 참여 스타트업 모집</t>
-  </si>
-  <si>
-    <t>오송첨단의료산...</t>
   </si>
   <si>
     <t>GC녹십자 수요기술 관련 기술·아이디어를 보유한 창업 10년 이내 바이오 창업기업</t>
@@ -694,9 +610,6 @@
     <t>2026 충남 대학생 창업경진대회 참가희망자 모집</t>
   </si>
   <si>
-    <t>씨엔티테크(주...</t>
-  </si>
-  <si>
     <t>충남 내 대학 소속 대학(원)생 개인 또는 팀</t>
   </si>
   <si>
@@ -743,9 +656,6 @@
   </si>
   <si>
     <t>2026년 하반기 경기도여성창업보육센터 입주기업 모집공고</t>
-  </si>
-  <si>
-    <t>경기도일자리재...</t>
   </si>
   <si>
     <t>경기도 내 여성 예비창업자 또는 창업 3년 이내의 여성기업</t>
@@ -758,9 +668,6 @@
     <t>2026년 구미시 스타트업 필드 4차 입주기업 모집 공고</t>
   </si>
   <si>
-    <t>구미전자정보기...</t>
-  </si>
-  <si>
     <t>예비창업 또는 구미 소재(이전 계획 포함) 창업 7년 이내 기업</t>
   </si>
   <si>
@@ -774,9 +681,6 @@
     <t>(~ 9/4 마감) 2026년도 재도전응원본부 재창업 특화교육·컨설팅 프로그램 모집 공고</t>
   </si>
   <si>
-    <t>중소벤처기업진...</t>
-  </si>
-  <si>
     <t>폐업 이력이 있는 예비재창업자 또는 재창업자</t>
   </si>
   <si>
@@ -840,9 +744,6 @@
     <t>2026 이화여대 모두의 창업 2기 프로젝트 사업설명회</t>
   </si>
   <si>
-    <t>이화여자대학교...</t>
-  </si>
-  <si>
     <t>예비창업자 또는 업력 7년 이내 이종 창업 기업</t>
   </si>
   <si>
@@ -874,9 +775,6 @@
   </si>
   <si>
     <t>「2026년 제3회 부기테크 투자쇼」상담회 참가기업 모집공고</t>
-  </si>
-  <si>
-    <t>부산기술창업투...</t>
   </si>
   <si>
     <t>부·울·경 소재 또는 부산 이전 수요가 있는 기술기반 기업</t>
@@ -1000,9 +898,6 @@
     <t>2026년 한국지역난방공사 창업·벤처기업 지원사업 참여기업 모집</t>
   </si>
   <si>
-    <t>(재)한국청년...</t>
-  </si>
-  <si>
     <t>공고일 기준 창업 7년 이내 창업기업 또는 벤처기업</t>
   </si>
   <si>
@@ -1016,9 +911,6 @@
     <t>달서구 중장년 기술창업센터 입주기업 모집</t>
   </si>
   <si>
-    <t>대구광역시 달...</t>
-  </si>
-  <si>
     <t>창업 3년 이내 만 40세 이상 중장년 또는 창업 7년 이내 예비/초기창업자</t>
   </si>
   <si>
@@ -1040,9 +932,6 @@
     <t>소공인 아카데미 4차 교육(소공인을 위한 특허 활용 전략)</t>
   </si>
   <si>
-    <t>(재)화성산업...</t>
-  </si>
-  <si>
     <t>화성시 기업 임직원 및 화성시민(예비창업자)</t>
   </si>
   <si>
@@ -1068,9 +957,6 @@
   </si>
   <si>
     <t>2026년 한국외대 창업보육센터 입주기업 모집 공고</t>
-  </si>
-  <si>
-    <t>한국외국어대학...</t>
   </si>
   <si>
     <t>예비창업자 및 3년 미만 창업기업</t>
@@ -1227,9 +1113,6 @@
     <t>국내 특허(IP) 보유기업 투자&amp;사업화 스케일업 지원사업</t>
   </si>
   <si>
-    <t>(주)엠비즈플...</t>
-  </si>
-  <si>
     <t>국내 특허 등록 또는 출원 중인 특허를 보유한 스타트업 및 중소기업</t>
   </si>
   <si>
@@ -1239,9 +1122,6 @@
     <t>2026 K-라이프스타일 페스타 with 메가쇼 참가기업(소상공인) 모집(~8/31(월)까지)</t>
   </si>
   <si>
-    <t>중소상공인희망...</t>
-  </si>
-  <si>
     <t>유통·판로를 확대하고자 메가쇼 참가를 희망하는 소상공인 기업</t>
   </si>
   <si>
@@ -1266,9 +1146,6 @@
     <t>2026년 컴퍼니빌더형 기술·경영 컨설팅 지원사업 TechBiz Venture Clinic 참가 기업 모집</t>
   </si>
   <si>
-    <t>(주)단국대학...</t>
-  </si>
-  <si>
     <t>공공기술 및 대학 보유 기술을 활용하고자 하는 예비창업자 및 창업 7년 이내 스타트업</t>
   </si>
   <si>
@@ -1281,9 +1158,6 @@
     <t>2026 제조 스타트업 멘토링 데이</t>
   </si>
   <si>
-    <t>주식회사볼트앤...</t>
-  </si>
-  <si>
     <t>(예비)창업자 및 기술창업에 관심 있는 누구나</t>
   </si>
   <si>
@@ -1291,9 +1165,6 @@
   </si>
   <si>
     <t>[환경재단] 2027 어스샷 상 혁신 환경 솔루션 공모</t>
-  </si>
-  <si>
-    <t>재단법인 환경...</t>
   </si>
   <si>
     <t>영향력 있는 혁신적 환경 솔루션을 보유한 국내 단체 및 기업/기관</t>
@@ -1330,6 +1201,138 @@
   <si>
     <t>오픈이노베이션
 PoC 최대 9천만원</t>
+  </si>
+  <si>
+    <t>한국전자정보통신산업진흥회</t>
+  </si>
+  <si>
+    <t>한국인터넷진흥원</t>
+  </si>
+  <si>
+    <t>에너지밸리기업개발원</t>
+  </si>
+  <si>
+    <t>광운대학교산학협력단</t>
+  </si>
+  <si>
+    <t>부산창조경제혁신센터</t>
+  </si>
+  <si>
+    <t>구로구 청년창업지원센터</t>
+  </si>
+  <si>
+    <t>코레일유통(주)</t>
+  </si>
+  <si>
+    <t>세종창조경제혁신센터</t>
+  </si>
+  <si>
+    <t>인천대학교</t>
+  </si>
+  <si>
+    <t>한국산림복지진흥원</t>
+  </si>
+  <si>
+    <t>한국성장금융투자운용</t>
+  </si>
+  <si>
+    <t>대구디지털혁신진흥원</t>
+  </si>
+  <si>
+    <t>중앙대학교 산학협력단</t>
+  </si>
+  <si>
+    <t>숭실대학교산학협력단</t>
+  </si>
+  <si>
+    <t>대전창조경제혁신센터</t>
+  </si>
+  <si>
+    <t>충남신용보증재단</t>
+  </si>
+  <si>
+    <t>(사) 타이드 인스티튜트</t>
+  </si>
+  <si>
+    <t>서울여자대학교 산학협력단</t>
+  </si>
+  <si>
+    <t>오송첨단의료산업진흥재단</t>
+  </si>
+  <si>
+    <t>강동구 청년해냄센터</t>
+  </si>
+  <si>
+    <t>(재)경기도경제과학진흥원</t>
+  </si>
+  <si>
+    <t>씨엔티테크(주)</t>
+  </si>
+  <si>
+    <t>경기도일자리재단</t>
+  </si>
+  <si>
+    <t>구미전자정보기술원</t>
+  </si>
+  <si>
+    <t>중소벤처기업진흥공단</t>
+  </si>
+  <si>
+    <t>차세대융합기술연구원</t>
+  </si>
+  <si>
+    <t>이화여자대학교산학협력단</t>
+  </si>
+  <si>
+    <t>부산기술창업투자원</t>
+  </si>
+  <si>
+    <t>(재)경기도경제과학진험원</t>
+  </si>
+  <si>
+    <t>해양수산과학기술진흥원</t>
+  </si>
+  <si>
+    <t>(재)한국청년기업가정신재단</t>
+  </si>
+  <si>
+    <t>대구광역시 달서구청</t>
+  </si>
+  <si>
+    <t>(재)화성산업진흥원</t>
+  </si>
+  <si>
+    <t>한국외국어대학교연구산학협력단</t>
+  </si>
+  <si>
+    <t>한국전파진흥협회</t>
+  </si>
+  <si>
+    <t>벤처박스주식회사</t>
+  </si>
+  <si>
+    <t>(주)엠와이소셜컴퍼니</t>
+  </si>
+  <si>
+    <t>(주)엠비즈플래닛(혁신기술경영지원센터)</t>
+  </si>
+  <si>
+    <t>중소상공인희망재단</t>
+  </si>
+  <si>
+    <t>(주)단국대학교 기술지주회사</t>
+  </si>
+  <si>
+    <t>주식회사볼트앤너트</t>
+  </si>
+  <si>
+    <t>재단법인 환경재단</t>
+  </si>
+  <si>
+    <t>주식회사 유디임팩트</t>
+  </si>
+  <si>
+    <t>신한금융희망재단</t>
   </si>
 </sst>
 </file>
@@ -1415,19 +1418,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1777,13 +1780,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>3</v>
@@ -1806,25 +1809,25 @@
         <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>86</v>
+        <v>384</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="I3" s="2">
         <v>2</v>
@@ -1832,57 +1835,57 @@
     </row>
     <row r="4" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>86</v>
+        <v>384</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="82" x14ac:dyDescent="0.45">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A5" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>94</v>
+        <v>385</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="I5" s="2">
         <v>1</v>
@@ -1890,28 +1893,28 @@
     </row>
     <row r="6" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A6" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>100</v>
+        <v>386</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="I6" s="2">
         <v>2</v>
@@ -1919,28 +1922,28 @@
     </row>
     <row r="7" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A7" s="3" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="I7" s="2">
         <v>1</v>
@@ -1948,28 +1951,28 @@
     </row>
     <row r="8" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>100</v>
+        <v>386</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="I8" s="2">
         <v>3</v>
@@ -1977,89 +1980,89 @@
     </row>
     <row r="9" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A9" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>15</v>
+        <v>387</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="82" x14ac:dyDescent="0.45">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A10" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A11" s="3" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>64</v>
+        <v>388</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
@@ -2067,54 +2070,54 @@
         <v>8</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>22</v>
+        <v>389</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="82" x14ac:dyDescent="0.45">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A13" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>126</v>
+        <v>390</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="I13" s="2">
         <v>2</v>
@@ -2122,118 +2125,118 @@
     </row>
     <row r="14" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A14" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>131</v>
+        <v>391</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A15" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>135</v>
+        <v>392</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>136</v>
+        <v>117</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A16" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>138</v>
+        <v>119</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>139</v>
+        <v>393</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A17" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.45">
@@ -2241,13 +2244,13 @@
         <v>1</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>3</v>
@@ -2267,28 +2270,28 @@
     </row>
     <row r="19" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A19" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="I19" s="2">
         <v>4</v>
@@ -2296,60 +2299,60 @@
     </row>
     <row r="20" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A20" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>152</v>
+        <v>394</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>154</v>
+        <v>133</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="102.5" x14ac:dyDescent="0.45">
       <c r="A21" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>157</v>
+        <v>395</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>159</v>
+        <v>137</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="82" x14ac:dyDescent="0.45">
@@ -2357,25 +2360,25 @@
         <v>8</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>160</v>
+        <v>138</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>81</v>
+        <v>396</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>161</v>
+        <v>139</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>162</v>
+        <v>140</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>163</v>
+        <v>141</v>
       </c>
       <c r="I22" s="2">
         <v>2</v>
@@ -2386,25 +2389,25 @@
         <v>8</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>164</v>
+        <v>142</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>81</v>
+        <v>396</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>161</v>
+        <v>139</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>162</v>
+        <v>140</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="I23" s="2">
         <v>2</v>
@@ -2412,60 +2415,60 @@
     </row>
     <row r="24" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A24" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>166</v>
+        <v>144</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>167</v>
+        <v>397</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="102.5" x14ac:dyDescent="0.45">
       <c r="A25" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>171</v>
+        <v>148</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>172</v>
+        <v>398</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="82" x14ac:dyDescent="0.45">
@@ -2473,54 +2476,54 @@
         <v>8</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>175</v>
+        <v>151</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>176</v>
+        <v>152</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>177</v>
+        <v>153</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>178</v>
+        <v>154</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A27" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>179</v>
+        <v>155</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>180</v>
+        <v>156</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>181</v>
+        <v>157</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>182</v>
+        <v>158</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>183</v>
+        <v>159</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="I27" s="2">
         <v>1</v>
@@ -2528,60 +2531,60 @@
     </row>
     <row r="28" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A28" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>185</v>
+        <v>161</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>186</v>
+        <v>399</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>187</v>
+        <v>162</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>188</v>
+        <v>163</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A29" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>189</v>
+        <v>164</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>190</v>
+        <v>400</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>191</v>
+        <v>165</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>192</v>
+        <v>166</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
@@ -2589,25 +2592,25 @@
         <v>8</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>193</v>
+        <v>167</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>194</v>
+        <v>401</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>195</v>
+        <v>168</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>196</v>
+        <v>169</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>197</v>
+        <v>170</v>
       </c>
       <c r="I30" s="2">
         <v>2</v>
@@ -2615,57 +2618,57 @@
     </row>
     <row r="31" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A31" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>198</v>
+        <v>171</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>81</v>
+        <v>396</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>199</v>
+        <v>172</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="82" x14ac:dyDescent="0.45">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A32" s="3" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>202</v>
+        <v>402</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>203</v>
+        <v>175</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>204</v>
+        <v>176</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>205</v>
+        <v>177</v>
       </c>
       <c r="I32" s="2">
         <v>4</v>
@@ -2673,31 +2676,31 @@
     </row>
     <row r="33" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A33" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>206</v>
+        <v>178</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>59</v>
+        <v>403</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>207</v>
+        <v>179</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>208</v>
+        <v>180</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.45">
@@ -2705,13 +2708,13 @@
         <v>1</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>3</v>
@@ -2731,31 +2734,31 @@
     </row>
     <row r="35" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A35" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>209</v>
+        <v>181</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>38</v>
+        <v>404</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>210</v>
+        <v>182</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>211</v>
+        <v>183</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
@@ -2763,25 +2766,25 @@
         <v>8</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>212</v>
+        <v>184</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>213</v>
+        <v>185</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>214</v>
+        <v>186</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>215</v>
+        <v>187</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>216</v>
+        <v>188</v>
       </c>
       <c r="I36" s="2">
         <v>2</v>
@@ -2789,28 +2792,28 @@
     </row>
     <row r="37" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A37" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>217</v>
+        <v>189</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>218</v>
+        <v>405</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>219</v>
+        <v>190</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>220</v>
+        <v>191</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>221</v>
+        <v>192</v>
       </c>
       <c r="I37" s="2">
         <v>1</v>
@@ -2818,28 +2821,28 @@
     </row>
     <row r="38" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A38" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>222</v>
+        <v>193</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>223</v>
+        <v>194</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>224</v>
+        <v>195</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>225</v>
+        <v>196</v>
       </c>
       <c r="I38" s="2">
         <v>4</v>
@@ -2847,60 +2850,60 @@
     </row>
     <row r="39" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A39" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>226</v>
+        <v>197</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>227</v>
+        <v>198</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>228</v>
+        <v>199</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>229</v>
+        <v>200</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A40" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>230</v>
+        <v>201</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>231</v>
+        <v>202</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>232</v>
+        <v>203</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>233</v>
+        <v>204</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
@@ -2908,25 +2911,25 @@
         <v>8</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>234</v>
+        <v>205</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>235</v>
+        <v>406</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>236</v>
+        <v>206</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>237</v>
+        <v>207</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>233</v>
+        <v>204</v>
       </c>
       <c r="I41" s="2">
         <v>2</v>
@@ -2937,25 +2940,25 @@
         <v>8</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>238</v>
+        <v>208</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>239</v>
+        <v>407</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>240</v>
+        <v>209</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>241</v>
+        <v>210</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>242</v>
+        <v>211</v>
       </c>
       <c r="I42" s="2">
         <v>2</v>
@@ -2963,57 +2966,57 @@
     </row>
     <row r="43" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A43" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>243</v>
+        <v>212</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>244</v>
+        <v>408</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>245</v>
+        <v>213</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>246</v>
+        <v>214</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A44" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>247</v>
+        <v>215</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>248</v>
+        <v>216</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>249</v>
+        <v>217</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>250</v>
+        <v>218</v>
       </c>
       <c r="I44" s="2">
         <v>1</v>
@@ -3021,86 +3024,86 @@
     </row>
     <row r="45" spans="1:9" ht="102.5" x14ac:dyDescent="0.45">
       <c r="A45" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>251</v>
+        <v>219</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>49</v>
+        <v>409</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>252</v>
+        <v>220</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>253</v>
+        <v>221</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A46" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>254</v>
+        <v>222</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>255</v>
+        <v>223</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>257</v>
+        <v>225</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A47" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G47" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B47" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="G47" s="4" t="s">
-        <v>63</v>
-      </c>
       <c r="H47" s="3" t="s">
-        <v>261</v>
+        <v>229</v>
       </c>
       <c r="I47" s="2">
         <v>1</v>
@@ -3108,60 +3111,60 @@
     </row>
     <row r="48" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A48" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>262</v>
+        <v>230</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>263</v>
+        <v>231</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>264</v>
+        <v>232</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A49" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>265</v>
+        <v>233</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>266</v>
+        <v>410</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>267</v>
+        <v>234</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>268</v>
+        <v>235</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.45">
@@ -3169,13 +3172,13 @@
         <v>1</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>3</v>
@@ -3195,115 +3198,115 @@
     </row>
     <row r="51" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A51" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>269</v>
+        <v>236</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>270</v>
+        <v>237</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>271</v>
+        <v>238</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>272</v>
+        <v>239</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A52" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>273</v>
+        <v>240</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>38</v>
+        <v>404</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>274</v>
+        <v>241</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>275</v>
+        <v>242</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>276</v>
+        <v>243</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A53" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>277</v>
+        <v>244</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>278</v>
+        <v>411</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>279</v>
+        <v>245</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>280</v>
+        <v>246</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="123" x14ac:dyDescent="0.45">
       <c r="A54" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>281</v>
+        <v>247</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>282</v>
+        <v>248</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>283</v>
+        <v>249</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>284</v>
+        <v>250</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>285</v>
+        <v>251</v>
       </c>
       <c r="I54" s="2">
         <v>2</v>
@@ -3314,25 +3317,25 @@
         <v>8</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>286</v>
+        <v>252</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>287</v>
+        <v>253</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>288</v>
+        <v>254</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>289</v>
+        <v>255</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="I55" s="2">
         <v>1</v>
@@ -3343,144 +3346,144 @@
         <v>8</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>292</v>
+        <v>258</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>293</v>
+        <v>259</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A57" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>294</v>
+        <v>260</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>38</v>
+        <v>412</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>295</v>
+        <v>261</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>296</v>
+        <v>262</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="102.5" x14ac:dyDescent="0.45">
       <c r="A58" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>297</v>
+        <v>263</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>298</v>
+        <v>264</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>299</v>
+        <v>265</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A59" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>300</v>
+        <v>266</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>34</v>
+        <v>413</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>301</v>
+        <v>267</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>302</v>
+        <v>268</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A60" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>303</v>
+        <v>269</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>304</v>
+        <v>270</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>305</v>
+        <v>271</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>306</v>
+        <v>272</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>307</v>
+        <v>273</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
@@ -3488,141 +3491,141 @@
         <v>8</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>308</v>
+        <v>274</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>287</v>
+        <v>253</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>309</v>
+        <v>275</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>310</v>
+        <v>276</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A62" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>311</v>
+        <v>277</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>312</v>
+        <v>278</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>313</v>
+        <v>279</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>314</v>
+        <v>280</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A63" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>315</v>
+        <v>281</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>218</v>
+        <v>405</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>316</v>
+        <v>282</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>317</v>
+        <v>283</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A64" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>318</v>
+        <v>284</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>319</v>
+        <v>414</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>320</v>
+        <v>285</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>321</v>
+        <v>286</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>322</v>
+        <v>287</v>
       </c>
       <c r="I64" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="82" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A65" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>323</v>
+        <v>288</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>324</v>
+        <v>415</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>325</v>
+        <v>289</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>326</v>
+        <v>290</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>327</v>
+        <v>291</v>
       </c>
       <c r="I65" s="2">
         <v>2</v>
@@ -3633,13 +3636,13 @@
         <v>1</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>3</v>
@@ -3662,57 +3665,57 @@
         <v>8</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>328</v>
+        <v>292</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>329</v>
+        <v>293</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>330</v>
+        <v>294</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A68" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>331</v>
+        <v>295</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>332</v>
+        <v>416</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>333</v>
+        <v>296</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>334</v>
+        <v>297</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
@@ -3720,25 +3723,25 @@
         <v>8</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>335</v>
+        <v>298</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>336</v>
+        <v>299</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>337</v>
+        <v>300</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>338</v>
+        <v>301</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>339</v>
+        <v>302</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>340</v>
+        <v>303</v>
       </c>
       <c r="I69" s="2">
         <v>2</v>
@@ -3749,25 +3752,25 @@
         <v>8</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>341</v>
+        <v>304</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>342</v>
+        <v>417</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>343</v>
+        <v>305</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>344</v>
+        <v>306</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>345</v>
+        <v>307</v>
       </c>
       <c r="I70" s="2">
         <v>2</v>
@@ -3778,28 +3781,28 @@
         <v>8</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>346</v>
+        <v>308</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>347</v>
+        <v>309</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>348</v>
+        <v>310</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="82" x14ac:dyDescent="0.45">
@@ -3807,25 +3810,25 @@
         <v>8</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>349</v>
+        <v>311</v>
       </c>
       <c r="C72" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E72" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="E72" s="3" t="s">
+      <c r="F72" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F72" s="3" t="s">
+      <c r="G72" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G72" s="4" t="s">
+      <c r="H72" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>13</v>
       </c>
       <c r="I72" s="2">
         <v>2</v>
@@ -3833,60 +3836,60 @@
     </row>
     <row r="73" spans="1:9" ht="143.5" x14ac:dyDescent="0.45">
       <c r="A73" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>351</v>
+        <v>313</v>
       </c>
       <c r="C73" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G73" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D73" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="E73" s="3" t="s">
+      <c r="H73" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F73" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G73" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H73" s="3" t="s">
-        <v>18</v>
-      </c>
       <c r="I73" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="102.5" x14ac:dyDescent="0.45">
       <c r="A74" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>353</v>
+        <v>315</v>
       </c>
       <c r="C74" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G74" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H74" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D74" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="E74" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F74" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G74" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H74" s="3" t="s">
-        <v>21</v>
-      </c>
       <c r="I74" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="102.5" x14ac:dyDescent="0.45">
@@ -3894,199 +3897,199 @@
         <v>8</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>355</v>
+        <v>317</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>22</v>
+        <v>389</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>356</v>
+        <v>318</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A76" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G76" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B76" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="C76" s="3" t="s">
+      <c r="H76" s="3" t="s">
         <v>26</v>
-      </c>
-      <c r="D76" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="E76" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="F76" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G76" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>29</v>
       </c>
       <c r="I76" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="82" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A77" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G77" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H77" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B77" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D77" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="E77" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F77" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G77" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="H77" s="3" t="s">
-        <v>36</v>
-      </c>
       <c r="I77" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A78" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>38</v>
+        <v>404</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>361</v>
+        <v>323</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A79" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>362</v>
+        <v>324</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>363</v>
+        <v>325</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A80" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>364</v>
+        <v>326</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>365</v>
+        <v>327</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="81" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A81" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G81" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H81" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D81" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="E81" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="F81" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G81" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="H81" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="I81" s="2">
         <v>3</v>
@@ -4097,13 +4100,13 @@
         <v>1</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="C82" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>3</v>
@@ -4123,28 +4126,28 @@
     </row>
     <row r="83" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A83" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>369</v>
+        <v>331</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>370</v>
+        <v>332</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>371</v>
+        <v>333</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>372</v>
+        <v>334</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>373</v>
+        <v>335</v>
       </c>
       <c r="I83" s="2">
         <v>1</v>
@@ -4152,28 +4155,28 @@
     </row>
     <row r="84" spans="1:9" ht="102.5" x14ac:dyDescent="0.45">
       <c r="A84" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>374</v>
+        <v>336</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>375</v>
+        <v>337</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>376</v>
+        <v>338</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>377</v>
+        <v>339</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>378</v>
+        <v>340</v>
       </c>
       <c r="I84" s="2">
         <v>3</v>
@@ -4181,28 +4184,28 @@
     </row>
     <row r="85" spans="1:9" ht="102.5" x14ac:dyDescent="0.45">
       <c r="A85" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>379</v>
+        <v>341</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>380</v>
+        <v>342</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>381</v>
+        <v>343</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>382</v>
+        <v>344</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>177</v>
+        <v>153</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>383</v>
+        <v>345</v>
       </c>
       <c r="I85" s="2">
         <v>1</v>
@@ -4210,115 +4213,115 @@
     </row>
     <row r="86" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A86" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>384</v>
+        <v>346</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>79</v>
+        <v>420</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>385</v>
+        <v>347</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>386</v>
+        <v>348</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A87" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>387</v>
+        <v>349</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>388</v>
+        <v>350</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>389</v>
+        <v>351</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>390</v>
+        <v>352</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>391</v>
+        <v>353</v>
       </c>
       <c r="I87" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="82" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A88" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>392</v>
+        <v>354</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>393</v>
+        <v>421</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>394</v>
+        <v>355</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>395</v>
+        <v>356</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="102.5" x14ac:dyDescent="0.45">
       <c r="A89" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>396</v>
+        <v>357</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>397</v>
+        <v>422</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>398</v>
+        <v>358</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>399</v>
+        <v>359</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>395</v>
+        <v>356</v>
       </c>
       <c r="I89" s="2">
         <v>1</v>
@@ -4326,28 +4329,28 @@
     </row>
     <row r="90" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A90" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>400</v>
+        <v>360</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>401</v>
+        <v>361</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>402</v>
+        <v>362</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>403</v>
+        <v>363</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>404</v>
+        <v>364</v>
       </c>
       <c r="I90" s="2">
         <v>1</v>
@@ -4355,86 +4358,86 @@
     </row>
     <row r="91" spans="1:9" ht="102.5" x14ac:dyDescent="0.45">
       <c r="A91" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>405</v>
+        <v>365</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>406</v>
+        <v>423</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>407</v>
+        <v>366</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>408</v>
+        <v>367</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>409</v>
+        <v>368</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="92" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A92" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>410</v>
+        <v>369</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>411</v>
+        <v>424</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>412</v>
+        <v>370</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>413</v>
+        <v>371</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="93" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A93" s="3" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>414</v>
+        <v>372</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>416</v>
+        <v>373</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>417</v>
+        <v>374</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>418</v>
+        <v>375</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>413</v>
+        <v>371</v>
       </c>
       <c r="I93" s="2">
         <v>5</v>
@@ -4442,57 +4445,57 @@
     </row>
     <row r="94" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A94" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>419</v>
+        <v>376</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>48</v>
+        <v>426</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>420</v>
+        <v>377</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="95" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A95" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>421</v>
+        <v>378</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>422</v>
+        <v>379</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="I95" s="2">
         <v>1</v>
@@ -4500,57 +4503,57 @@
     </row>
     <row r="96" spans="1:9" ht="102.5" x14ac:dyDescent="0.45">
       <c r="A96" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>423</v>
+        <v>380</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>76</v>
+        <v>427</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>424</v>
+        <v>381</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="I96" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="97" spans="1:9" ht="82" x14ac:dyDescent="0.45">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A97" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>79</v>
+        <v>420</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>425</v>
+        <v>382</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>426</v>
+        <v>383</v>
       </c>
       <c r="F97" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="I97" s="2">
         <v>4</v>

--- a/assets/01_엠엔엘뉴스.xlsx
+++ b/assets/01_엠엔엘뉴스.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\공유 드라이브\00_RyanKim_김장길\07_방송_Broadcast\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3608D8A-1E26-4A2A-89C4-947F010E7113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CEB4B03-1834-4954-8840-F79B5A9D2942}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{13C56ADD-2978-4209-B5B1-7D56087C6640}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="828" uniqueCount="428">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="828" uniqueCount="427">
   <si>
     <t>2026년 9월 1주차</t>
   </si>
@@ -65,6 +65,9 @@
     <t>시설·공간·보육</t>
   </si>
   <si>
+    <t>한국전파진흥협...</t>
+  </si>
+  <si>
     <t>서울 강서,독립,유료</t>
   </si>
   <si>
@@ -80,6 +83,9 @@
     <t>행사·네트워크</t>
   </si>
   <si>
+    <t>광운대학교산학...</t>
+  </si>
+  <si>
     <t>-</t>
   </si>
   <si>
@@ -98,6 +104,9 @@
     <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?pbancClssCd=PBC010&amp;schM=view&amp;pbancSn=178976</t>
   </si>
   <si>
+    <t>구로구 청년창...</t>
+  </si>
+  <si>
     <t>2026.9.2.</t>
   </si>
   <si>
@@ -131,6 +140,9 @@
     <t>2026 예비오션스타 기업 모집 공고</t>
   </si>
   <si>
+    <t>해양수산과학기...</t>
+  </si>
+  <si>
     <t>2026.9.11.</t>
   </si>
   <si>
@@ -140,6 +152,9 @@
     <t>모두의 창업 멘토가 알려주는 사업계획서 작성 방법 특강</t>
   </si>
   <si>
+    <t>(재)경기도경...</t>
+  </si>
+  <si>
     <t>2026.8.31.</t>
   </si>
   <si>
@@ -158,12 +173,21 @@
     <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?pbancClssCd=PBC010&amp;schM=view&amp;pbancSn=178970</t>
   </si>
   <si>
+    <t>벤처박스주식회...</t>
+  </si>
+  <si>
     <t>2026.9.1.</t>
   </si>
   <si>
     <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?pbancClssCd=PBC010&amp;schM=view&amp;pbancSn=178972</t>
   </si>
   <si>
+    <t>주식회사 유디...</t>
+  </si>
+  <si>
+    <t>차세대융합기술...</t>
+  </si>
+  <si>
     <t>2026.9.4.</t>
   </si>
   <si>
@@ -191,6 +215,9 @@
     <t>2026.9.8.</t>
   </si>
   <si>
+    <t>강동구 청년해...</t>
+  </si>
+  <si>
     <t>2026.9.30.</t>
   </si>
   <si>
@@ -203,6 +230,9 @@
     <t>2026.9.7.</t>
   </si>
   <si>
+    <t>부산창조경제혁...</t>
+  </si>
+  <si>
     <t>2026.8.28.</t>
   </si>
   <si>
@@ -236,15 +266,24 @@
     <t>포켓컴퍼니</t>
   </si>
   <si>
+    <t>신한금융희망재...</t>
+  </si>
+  <si>
     <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?pbancClssCd=PBC020&amp;schM=view&amp;pbancSn=178942</t>
   </si>
   <si>
     <t>2026 현대모비스 CSV 오픈 이노베이션 참여 기업 모집</t>
   </si>
   <si>
+    <t>(주)엠와이소...</t>
+  </si>
+  <si>
     <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?pbancClssCd=PBC020&amp;schM=view&amp;pbancSn=178951</t>
   </si>
   <si>
+    <t>중앙대학교 산...</t>
+  </si>
+  <si>
     <t>경북</t>
   </si>
   <si>
@@ -257,6 +296,9 @@
     <t>26년 AI·스마트전자제품 금형지원 기업모집</t>
   </si>
   <si>
+    <t>한국전자정보통...</t>
+  </si>
+  <si>
     <t>전자기기 기반 제품을 개발, 제조하는 창업기업 및 중소기업</t>
   </si>
   <si>
@@ -278,6 +320,9 @@
     <t>싱가포르 현지 진출 지원 국내 블록체인 기업 모집</t>
   </si>
   <si>
+    <t>한국인터넷진흥...</t>
+  </si>
+  <si>
     <t>블록체인 기술 보유 및 해외 진출 역량이 있는 블록체인 중소기업 또는 스타트업</t>
   </si>
   <si>
@@ -293,6 +338,9 @@
     <t>2026년 한전KPS 창업벤처기업 육성 지원사업 참여기업 모집안내</t>
   </si>
   <si>
+    <t>에너지밸리기업...</t>
+  </si>
+  <si>
     <t>에너지, 탄소중립/친환경 분야 창업 7년 미만 또는 벤처기업</t>
   </si>
   <si>
@@ -366,6 +414,9 @@
   </si>
   <si>
     <t>[코레일유통/본사] 제11차 청년창업 제휴사업자 모집공고</t>
+  </si>
+  <si>
+    <t>코레일유통(주...</t>
   </si>
   <si>
     <t>만 18세 이상 39세 이하 예비창업자 또는 창업 3년 이하 소기업 대표자</t>
@@ -381,6 +432,9 @@
     <t>2026년 세종 스타트업 원스톱 지원센터 아카데미 3차</t>
   </si>
   <si>
+    <t>세종창조경제혁...</t>
+  </si>
+  <si>
     <t>세종시 소재 예비창업기업 또는 사업 거점 보유 기업</t>
   </si>
   <si>
@@ -390,6 +444,9 @@
     <t>[인천대학교] 모두의창업 프로젝트(2차) 모집홍보 교육 『AI와 함께하는 BM 스쿨』</t>
   </si>
   <si>
+    <t>국립대학법인 ...</t>
+  </si>
+  <si>
     <t>예비창업자 또는 업력 7년 이내 기창업자</t>
   </si>
   <si>
@@ -399,6 +456,9 @@
     <t>2026년 민간 산림복지 창업 아카데미[1차] 참가자 모집</t>
   </si>
   <si>
+    <t>한국산림복지진...</t>
+  </si>
+  <si>
     <t>산림복지전문업 창업에 관심이 있는 예비창업자</t>
   </si>
   <si>
@@ -435,6 +495,9 @@
     <t>코리아 핀테크 위크 2026 「핀테크 스타트업 1:1 투자 밋업」 참여기업 모집</t>
   </si>
   <si>
+    <t>한국성장금융투...</t>
+  </si>
+  <si>
     <t>핀테크 스타트업 또는 핀테크 영역 사업 확장 희망 스타트업</t>
   </si>
   <si>
@@ -447,6 +510,9 @@
     <t>2026년 대구 콘텐츠 스케일업 액셀러레이팅 프로그램 지원사업 참여기업 추가 모집 공고</t>
   </si>
   <si>
+    <t>대구디지털혁신...</t>
+  </si>
+  <si>
     <t>본점 소재지가 대구인 업력 7년 미만 콘텐츠 기업</t>
   </si>
   <si>
@@ -474,6 +540,9 @@
     <t>[숭실대학교 캠퍼스타운] 2026 석·박사급 실험실 창업스쿨(유형2) 참여자 모집</t>
   </si>
   <si>
+    <t>숭실대학교산학...</t>
+  </si>
+  <si>
     <t>이공계 석·박사급 연구인력 및 예비창업자, 초기창업자</t>
   </si>
   <si>
@@ -486,6 +555,9 @@
     <t>2026년 대전 스타트업스쿨 스타트업 리딩클래스 (4회차 ㅣ 스타트업 IR &amp; 투자유치 마스터클래스)</t>
   </si>
   <si>
+    <t>대전창조경제혁...</t>
+  </si>
+  <si>
     <t>스타트업 역량 강화에 관심이 있는 누구나</t>
   </si>
   <si>
@@ -525,6 +597,9 @@
     <t>2026년 9월 동네창업학교 교육생 모집 공고</t>
   </si>
   <si>
+    <t>충남신용보증재...</t>
+  </si>
+  <si>
     <t>충남 내 창업 예정 청년 예비창업자 또는 충남 소재 청년 기창업자</t>
   </si>
   <si>
@@ -534,6 +609,9 @@
     <t>KAC 한국공항공사 항공산업분야 창업 인큐베이팅 프로그램</t>
   </si>
   <si>
+    <t>(사) 타이드...</t>
+  </si>
+  <si>
     <t>항공산업과 연계된 아이디어를 가진 예비창업자</t>
   </si>
   <si>
@@ -543,6 +621,9 @@
     <t>[서울여자대학교 창업보육센터] 신규 입주기업 모집 공고</t>
   </si>
   <si>
+    <t>서울여자대학교...</t>
+  </si>
+  <si>
     <t>예비창업자 또는 창업 7년 이내 기업</t>
   </si>
   <si>
@@ -562,6 +643,9 @@
   </si>
   <si>
     <t>2026년 충북 바이오 오픈이노베이션 사업 참여 스타트업 모집</t>
+  </si>
+  <si>
+    <t>오송첨단의료산...</t>
   </si>
   <si>
     <t>GC녹십자 수요기술 관련 기술·아이디어를 보유한 창업 10년 이내 바이오 창업기업</t>
@@ -610,6 +694,9 @@
     <t>2026 충남 대학생 창업경진대회 참가희망자 모집</t>
   </si>
   <si>
+    <t>씨엔티테크(주...</t>
+  </si>
+  <si>
     <t>충남 내 대학 소속 대학(원)생 개인 또는 팀</t>
   </si>
   <si>
@@ -656,6 +743,9 @@
   </si>
   <si>
     <t>2026년 하반기 경기도여성창업보육센터 입주기업 모집공고</t>
+  </si>
+  <si>
+    <t>경기도일자리재...</t>
   </si>
   <si>
     <t>경기도 내 여성 예비창업자 또는 창업 3년 이내의 여성기업</t>
@@ -668,6 +758,9 @@
     <t>2026년 구미시 스타트업 필드 4차 입주기업 모집 공고</t>
   </si>
   <si>
+    <t>구미전자정보기...</t>
+  </si>
+  <si>
     <t>예비창업 또는 구미 소재(이전 계획 포함) 창업 7년 이내 기업</t>
   </si>
   <si>
@@ -681,6 +774,9 @@
     <t>(~ 9/4 마감) 2026년도 재도전응원본부 재창업 특화교육·컨설팅 프로그램 모집 공고</t>
   </si>
   <si>
+    <t>중소벤처기업진...</t>
+  </si>
+  <si>
     <t>폐업 이력이 있는 예비재창업자 또는 재창업자</t>
   </si>
   <si>
@@ -744,6 +840,9 @@
     <t>2026 이화여대 모두의 창업 2기 프로젝트 사업설명회</t>
   </si>
   <si>
+    <t>이화여자대학교...</t>
+  </si>
+  <si>
     <t>예비창업자 또는 업력 7년 이내 이종 창업 기업</t>
   </si>
   <si>
@@ -775,6 +874,9 @@
   </si>
   <si>
     <t>「2026년 제3회 부기테크 투자쇼」상담회 참가기업 모집공고</t>
+  </si>
+  <si>
+    <t>부산기술창업투...</t>
   </si>
   <si>
     <t>부·울·경 소재 또는 부산 이전 수요가 있는 기술기반 기업</t>
@@ -898,6 +1000,9 @@
     <t>2026년 한국지역난방공사 창업·벤처기업 지원사업 참여기업 모집</t>
   </si>
   <si>
+    <t>(재)한국청년...</t>
+  </si>
+  <si>
     <t>공고일 기준 창업 7년 이내 창업기업 또는 벤처기업</t>
   </si>
   <si>
@@ -911,6 +1016,9 @@
     <t>달서구 중장년 기술창업센터 입주기업 모집</t>
   </si>
   <si>
+    <t>대구광역시 달...</t>
+  </si>
+  <si>
     <t>창업 3년 이내 만 40세 이상 중장년 또는 창업 7년 이내 예비/초기창업자</t>
   </si>
   <si>
@@ -932,6 +1040,9 @@
     <t>소공인 아카데미 4차 교육(소공인을 위한 특허 활용 전략)</t>
   </si>
   <si>
+    <t>(재)화성산업...</t>
+  </si>
+  <si>
     <t>화성시 기업 임직원 및 화성시민(예비창업자)</t>
   </si>
   <si>
@@ -957,6 +1068,9 @@
   </si>
   <si>
     <t>2026년 한국외대 창업보육센터 입주기업 모집 공고</t>
+  </si>
+  <si>
+    <t>한국외국어대학...</t>
   </si>
   <si>
     <t>예비창업자 및 3년 미만 창업기업</t>
@@ -1113,6 +1227,9 @@
     <t>국내 특허(IP) 보유기업 투자&amp;사업화 스케일업 지원사업</t>
   </si>
   <si>
+    <t>(주)엠비즈플...</t>
+  </si>
+  <si>
     <t>국내 특허 등록 또는 출원 중인 특허를 보유한 스타트업 및 중소기업</t>
   </si>
   <si>
@@ -1122,6 +1239,9 @@
     <t>2026 K-라이프스타일 페스타 with 메가쇼 참가기업(소상공인) 모집(~8/31(월)까지)</t>
   </si>
   <si>
+    <t>중소상공인희망...</t>
+  </si>
+  <si>
     <t>유통·판로를 확대하고자 메가쇼 참가를 희망하는 소상공인 기업</t>
   </si>
   <si>
@@ -1146,6 +1266,9 @@
     <t>2026년 컴퍼니빌더형 기술·경영 컨설팅 지원사업 TechBiz Venture Clinic 참가 기업 모집</t>
   </si>
   <si>
+    <t>(주)단국대학...</t>
+  </si>
+  <si>
     <t>공공기술 및 대학 보유 기술을 활용하고자 하는 예비창업자 및 창업 7년 이내 스타트업</t>
   </si>
   <si>
@@ -1158,6 +1281,9 @@
     <t>2026 제조 스타트업 멘토링 데이</t>
   </si>
   <si>
+    <t>주식회사볼트앤...</t>
+  </si>
+  <si>
     <t>(예비)창업자 및 기술창업에 관심 있는 누구나</t>
   </si>
   <si>
@@ -1165,6 +1291,9 @@
   </si>
   <si>
     <t>[환경재단] 2027 어스샷 상 혁신 환경 솔루션 공모</t>
+  </si>
+  <si>
+    <t>재단법인 환경...</t>
   </si>
   <si>
     <t>영향력 있는 혁신적 환경 솔루션을 보유한 국내 단체 및 기업/기관</t>
@@ -1201,138 +1330,6 @@
   <si>
     <t>오픈이노베이션
 PoC 최대 9천만원</t>
-  </si>
-  <si>
-    <t>한국전자정보통신산업진흥회</t>
-  </si>
-  <si>
-    <t>한국인터넷진흥원</t>
-  </si>
-  <si>
-    <t>에너지밸리기업개발원</t>
-  </si>
-  <si>
-    <t>광운대학교산학협력단</t>
-  </si>
-  <si>
-    <t>부산창조경제혁신센터</t>
-  </si>
-  <si>
-    <t>구로구 청년창업지원센터</t>
-  </si>
-  <si>
-    <t>코레일유통(주)</t>
-  </si>
-  <si>
-    <t>세종창조경제혁신센터</t>
-  </si>
-  <si>
-    <t>인천대학교</t>
-  </si>
-  <si>
-    <t>한국산림복지진흥원</t>
-  </si>
-  <si>
-    <t>한국성장금융투자운용</t>
-  </si>
-  <si>
-    <t>대구디지털혁신진흥원</t>
-  </si>
-  <si>
-    <t>중앙대학교 산학협력단</t>
-  </si>
-  <si>
-    <t>숭실대학교산학협력단</t>
-  </si>
-  <si>
-    <t>대전창조경제혁신센터</t>
-  </si>
-  <si>
-    <t>충남신용보증재단</t>
-  </si>
-  <si>
-    <t>(사) 타이드 인스티튜트</t>
-  </si>
-  <si>
-    <t>서울여자대학교 산학협력단</t>
-  </si>
-  <si>
-    <t>오송첨단의료산업진흥재단</t>
-  </si>
-  <si>
-    <t>강동구 청년해냄센터</t>
-  </si>
-  <si>
-    <t>(재)경기도경제과학진흥원</t>
-  </si>
-  <si>
-    <t>씨엔티테크(주)</t>
-  </si>
-  <si>
-    <t>경기도일자리재단</t>
-  </si>
-  <si>
-    <t>구미전자정보기술원</t>
-  </si>
-  <si>
-    <t>중소벤처기업진흥공단</t>
-  </si>
-  <si>
-    <t>차세대융합기술연구원</t>
-  </si>
-  <si>
-    <t>이화여자대학교산학협력단</t>
-  </si>
-  <si>
-    <t>부산기술창업투자원</t>
-  </si>
-  <si>
-    <t>(재)경기도경제과학진험원</t>
-  </si>
-  <si>
-    <t>해양수산과학기술진흥원</t>
-  </si>
-  <si>
-    <t>(재)한국청년기업가정신재단</t>
-  </si>
-  <si>
-    <t>대구광역시 달서구청</t>
-  </si>
-  <si>
-    <t>(재)화성산업진흥원</t>
-  </si>
-  <si>
-    <t>한국외국어대학교연구산학협력단</t>
-  </si>
-  <si>
-    <t>한국전파진흥협회</t>
-  </si>
-  <si>
-    <t>벤처박스주식회사</t>
-  </si>
-  <si>
-    <t>(주)엠와이소셜컴퍼니</t>
-  </si>
-  <si>
-    <t>(주)엠비즈플래닛(혁신기술경영지원센터)</t>
-  </si>
-  <si>
-    <t>중소상공인희망재단</t>
-  </si>
-  <si>
-    <t>(주)단국대학교 기술지주회사</t>
-  </si>
-  <si>
-    <t>주식회사볼트앤너트</t>
-  </si>
-  <si>
-    <t>재단법인 환경재단</t>
-  </si>
-  <si>
-    <t>주식회사 유디임팩트</t>
-  </si>
-  <si>
-    <t>신한금융희망재단</t>
   </si>
 </sst>
 </file>
@@ -1418,19 +1415,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1780,13 +1777,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>3</v>
@@ -1809,25 +1806,25 @@
         <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>384</v>
+        <v>86</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="I3" s="2">
         <v>2</v>
@@ -1835,57 +1832,57 @@
     </row>
     <row r="4" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>384</v>
+        <v>86</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A5" s="3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>385</v>
+        <v>94</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="I5" s="2">
         <v>1</v>
@@ -1893,28 +1890,28 @@
     </row>
     <row r="6" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A6" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>386</v>
+        <v>100</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="I6" s="2">
         <v>2</v>
@@ -1922,28 +1919,28 @@
     </row>
     <row r="7" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A7" s="3" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="I7" s="2">
         <v>1</v>
@@ -1951,28 +1948,28 @@
     </row>
     <row r="8" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>386</v>
+        <v>100</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="I8" s="2">
         <v>3</v>
@@ -1980,89 +1977,89 @@
     </row>
     <row r="9" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A9" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>387</v>
+        <v>15</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A10" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A11" s="3" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>388</v>
+        <v>64</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
@@ -2070,54 +2067,54 @@
         <v>8</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>389</v>
+        <v>22</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A13" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>390</v>
+        <v>126</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="I13" s="2">
         <v>2</v>
@@ -2125,118 +2122,118 @@
     </row>
     <row r="14" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A14" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>391</v>
+        <v>131</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A15" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>392</v>
+        <v>135</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A16" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>393</v>
+        <v>139</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A17" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>122</v>
+        <v>142</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>123</v>
+        <v>143</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>124</v>
+        <v>144</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>125</v>
+        <v>145</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.45">
@@ -2244,13 +2241,13 @@
         <v>1</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>3</v>
@@ -2270,28 +2267,28 @@
     </row>
     <row r="19" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A19" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>128</v>
+        <v>148</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="I19" s="2">
         <v>4</v>
@@ -2299,60 +2296,60 @@
     </row>
     <row r="20" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A20" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>394</v>
+        <v>152</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="102.5" x14ac:dyDescent="0.45">
       <c r="A21" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>395</v>
+        <v>157</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>137</v>
+        <v>159</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="82" x14ac:dyDescent="0.45">
@@ -2360,25 +2357,25 @@
         <v>8</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>396</v>
+        <v>81</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>141</v>
+        <v>163</v>
       </c>
       <c r="I22" s="2">
         <v>2</v>
@@ -2389,25 +2386,25 @@
         <v>8</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>142</v>
+        <v>164</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>396</v>
+        <v>81</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="I23" s="2">
         <v>2</v>
@@ -2415,60 +2412,60 @@
     </row>
     <row r="24" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A24" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>397</v>
+        <v>167</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>145</v>
+        <v>168</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>146</v>
+        <v>169</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>147</v>
+        <v>170</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="102.5" x14ac:dyDescent="0.45">
       <c r="A25" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>148</v>
+        <v>171</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>398</v>
+        <v>172</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>149</v>
+        <v>173</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>150</v>
+        <v>174</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="82" x14ac:dyDescent="0.45">
@@ -2476,54 +2473,54 @@
         <v>8</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>151</v>
+        <v>175</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>152</v>
+        <v>176</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>153</v>
+        <v>177</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>154</v>
+        <v>178</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A27" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>155</v>
+        <v>179</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>156</v>
+        <v>180</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>157</v>
+        <v>181</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>158</v>
+        <v>182</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>159</v>
+        <v>183</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>160</v>
+        <v>184</v>
       </c>
       <c r="I27" s="2">
         <v>1</v>
@@ -2531,60 +2528,60 @@
     </row>
     <row r="28" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A28" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>161</v>
+        <v>185</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>399</v>
+        <v>186</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>162</v>
+        <v>187</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>163</v>
+        <v>188</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A29" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>164</v>
+        <v>189</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>400</v>
+        <v>190</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>166</v>
+        <v>192</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
@@ -2592,25 +2589,25 @@
         <v>8</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>167</v>
+        <v>193</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>401</v>
+        <v>194</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>168</v>
+        <v>195</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>169</v>
+        <v>196</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>170</v>
+        <v>197</v>
       </c>
       <c r="I30" s="2">
         <v>2</v>
@@ -2618,57 +2615,57 @@
     </row>
     <row r="31" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A31" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>171</v>
+        <v>198</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>396</v>
+        <v>81</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>172</v>
+        <v>199</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A32" s="3" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>174</v>
+        <v>201</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>402</v>
+        <v>202</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>175</v>
+        <v>203</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>176</v>
+        <v>204</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>177</v>
+        <v>205</v>
       </c>
       <c r="I32" s="2">
         <v>4</v>
@@ -2676,31 +2673,31 @@
     </row>
     <row r="33" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A33" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>178</v>
+        <v>206</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>403</v>
+        <v>59</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>179</v>
+        <v>207</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>180</v>
+        <v>208</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.45">
@@ -2708,13 +2705,13 @@
         <v>1</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>3</v>
@@ -2734,31 +2731,31 @@
     </row>
     <row r="35" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A35" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>181</v>
+        <v>209</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>404</v>
+        <v>38</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>182</v>
+        <v>210</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>183</v>
+        <v>211</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
@@ -2766,25 +2763,25 @@
         <v>8</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>184</v>
+        <v>212</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>186</v>
+        <v>214</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>187</v>
+        <v>215</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>188</v>
+        <v>216</v>
       </c>
       <c r="I36" s="2">
         <v>2</v>
@@ -2792,28 +2789,28 @@
     </row>
     <row r="37" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A37" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>189</v>
+        <v>217</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>405</v>
+        <v>218</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>190</v>
+        <v>219</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>191</v>
+        <v>220</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>192</v>
+        <v>221</v>
       </c>
       <c r="I37" s="2">
         <v>1</v>
@@ -2821,28 +2818,28 @@
     </row>
     <row r="38" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A38" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>193</v>
+        <v>222</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>194</v>
+        <v>223</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>195</v>
+        <v>224</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>196</v>
+        <v>225</v>
       </c>
       <c r="I38" s="2">
         <v>4</v>
@@ -2850,60 +2847,60 @@
     </row>
     <row r="39" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A39" s="3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>197</v>
+        <v>226</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>198</v>
+        <v>227</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>199</v>
+        <v>228</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>200</v>
+        <v>229</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A40" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>201</v>
+        <v>230</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>202</v>
+        <v>231</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>203</v>
+        <v>232</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>204</v>
+        <v>233</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
@@ -2911,25 +2908,25 @@
         <v>8</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>205</v>
+        <v>234</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>406</v>
+        <v>235</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>206</v>
+        <v>236</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>207</v>
+        <v>237</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>204</v>
+        <v>233</v>
       </c>
       <c r="I41" s="2">
         <v>2</v>
@@ -2940,25 +2937,25 @@
         <v>8</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>208</v>
+        <v>238</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>407</v>
+        <v>239</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>209</v>
+        <v>240</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>210</v>
+        <v>241</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>211</v>
+        <v>242</v>
       </c>
       <c r="I42" s="2">
         <v>2</v>
@@ -2966,57 +2963,57 @@
     </row>
     <row r="43" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A43" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>212</v>
+        <v>243</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>408</v>
+        <v>244</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>213</v>
+        <v>245</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>214</v>
+        <v>246</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A44" s="3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>215</v>
+        <v>247</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>216</v>
+        <v>248</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>217</v>
+        <v>249</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>218</v>
+        <v>250</v>
       </c>
       <c r="I44" s="2">
         <v>1</v>
@@ -3024,86 +3021,86 @@
     </row>
     <row r="45" spans="1:9" ht="102.5" x14ac:dyDescent="0.45">
       <c r="A45" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>219</v>
+        <v>251</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>409</v>
+        <v>49</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>220</v>
+        <v>252</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>221</v>
+        <v>253</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A46" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>222</v>
+        <v>254</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>223</v>
+        <v>255</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>225</v>
+        <v>257</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A47" s="3" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>226</v>
+        <v>258</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>227</v>
+        <v>259</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>228</v>
+        <v>260</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>229</v>
+        <v>261</v>
       </c>
       <c r="I47" s="2">
         <v>1</v>
@@ -3111,60 +3108,60 @@
     </row>
     <row r="48" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A48" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>230</v>
+        <v>262</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>231</v>
+        <v>263</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>232</v>
+        <v>264</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A49" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>233</v>
+        <v>265</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>410</v>
+        <v>266</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>234</v>
+        <v>267</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>235</v>
+        <v>268</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.45">
@@ -3172,13 +3169,13 @@
         <v>1</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>3</v>
@@ -3198,115 +3195,115 @@
     </row>
     <row r="51" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A51" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>236</v>
+        <v>269</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>237</v>
+        <v>270</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>238</v>
+        <v>271</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>239</v>
+        <v>272</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A52" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>240</v>
+        <v>273</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>404</v>
+        <v>38</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>241</v>
+        <v>274</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>242</v>
+        <v>275</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>243</v>
+        <v>276</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A53" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>244</v>
+        <v>277</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>411</v>
+        <v>278</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>245</v>
+        <v>279</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>246</v>
+        <v>280</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="123" x14ac:dyDescent="0.45">
       <c r="A54" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>247</v>
+        <v>281</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>248</v>
+        <v>282</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>249</v>
+        <v>283</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>250</v>
+        <v>284</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>251</v>
+        <v>285</v>
       </c>
       <c r="I54" s="2">
         <v>2</v>
@@ -3317,25 +3314,25 @@
         <v>8</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>252</v>
+        <v>286</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>253</v>
+        <v>287</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>254</v>
+        <v>288</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>255</v>
+        <v>289</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>256</v>
+        <v>290</v>
       </c>
       <c r="I55" s="2">
         <v>1</v>
@@ -3346,144 +3343,144 @@
         <v>8</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>257</v>
+        <v>291</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>258</v>
+        <v>292</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>259</v>
+        <v>293</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A57" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>260</v>
+        <v>294</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>412</v>
+        <v>38</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>261</v>
+        <v>295</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>262</v>
+        <v>296</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="102.5" x14ac:dyDescent="0.45">
       <c r="A58" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>263</v>
+        <v>297</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>264</v>
+        <v>298</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>265</v>
+        <v>299</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A59" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>266</v>
+        <v>300</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>413</v>
+        <v>34</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>267</v>
+        <v>301</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>268</v>
+        <v>302</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A60" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>269</v>
+        <v>303</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>270</v>
+        <v>304</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>271</v>
+        <v>305</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>272</v>
+        <v>306</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>273</v>
+        <v>307</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
@@ -3491,141 +3488,141 @@
         <v>8</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>274</v>
+        <v>308</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>253</v>
+        <v>287</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>275</v>
+        <v>309</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>276</v>
+        <v>310</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A62" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>277</v>
+        <v>311</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>278</v>
+        <v>312</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>279</v>
+        <v>313</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>280</v>
+        <v>314</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A63" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>281</v>
+        <v>315</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>405</v>
+        <v>218</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>282</v>
+        <v>316</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>283</v>
+        <v>317</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A64" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>284</v>
+        <v>318</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>414</v>
+        <v>319</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>285</v>
+        <v>320</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>286</v>
+        <v>321</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>287</v>
+        <v>322</v>
       </c>
       <c r="I64" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A65" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>288</v>
+        <v>323</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>415</v>
+        <v>324</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>289</v>
+        <v>325</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>290</v>
+        <v>326</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>291</v>
+        <v>327</v>
       </c>
       <c r="I65" s="2">
         <v>2</v>
@@ -3636,13 +3633,13 @@
         <v>1</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>3</v>
@@ -3665,57 +3662,57 @@
         <v>8</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>292</v>
+        <v>328</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>293</v>
+        <v>329</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>294</v>
+        <v>330</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A68" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>295</v>
+        <v>331</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>416</v>
+        <v>332</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>296</v>
+        <v>333</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>297</v>
+        <v>334</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
@@ -3723,25 +3720,25 @@
         <v>8</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>298</v>
+        <v>335</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>299</v>
+        <v>336</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>300</v>
+        <v>337</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>301</v>
+        <v>338</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>302</v>
+        <v>339</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>303</v>
+        <v>340</v>
       </c>
       <c r="I69" s="2">
         <v>2</v>
@@ -3752,25 +3749,25 @@
         <v>8</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>304</v>
+        <v>341</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>417</v>
+        <v>342</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>305</v>
+        <v>343</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>306</v>
+        <v>344</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>307</v>
+        <v>345</v>
       </c>
       <c r="I70" s="2">
         <v>2</v>
@@ -3781,28 +3778,28 @@
         <v>8</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>308</v>
+        <v>346</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>309</v>
+        <v>347</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>310</v>
+        <v>348</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="82" x14ac:dyDescent="0.45">
@@ -3810,25 +3807,25 @@
         <v>8</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>311</v>
+        <v>349</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>418</v>
+        <v>9</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>312</v>
+        <v>350</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I72" s="2">
         <v>2</v>
@@ -3836,60 +3833,60 @@
     </row>
     <row r="73" spans="1:9" ht="143.5" x14ac:dyDescent="0.45">
       <c r="A73" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>313</v>
+        <v>351</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>387</v>
+        <v>15</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>314</v>
+        <v>352</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="102.5" x14ac:dyDescent="0.45">
       <c r="A74" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>315</v>
+        <v>353</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>316</v>
+        <v>354</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="102.5" x14ac:dyDescent="0.45">
@@ -3897,199 +3894,199 @@
         <v>8</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>317</v>
+        <v>355</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>389</v>
+        <v>22</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>318</v>
+        <v>356</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A76" s="3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>319</v>
+        <v>357</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>320</v>
+        <v>358</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>321</v>
+        <v>359</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="I76" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A77" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>413</v>
+        <v>34</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>322</v>
+        <v>360</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A78" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>404</v>
+        <v>38</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>323</v>
+        <v>361</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A79" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>324</v>
+        <v>362</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>325</v>
+        <v>363</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A80" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>326</v>
+        <v>364</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>327</v>
+        <v>365</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="81" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A81" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>328</v>
+        <v>366</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>419</v>
+        <v>45</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>329</v>
+        <v>367</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>330</v>
+        <v>368</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="I81" s="2">
         <v>3</v>
@@ -4100,13 +4097,13 @@
         <v>1</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="C82" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>3</v>
@@ -4126,28 +4123,28 @@
     </row>
     <row r="83" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A83" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>331</v>
+        <v>369</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>332</v>
+        <v>370</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>333</v>
+        <v>371</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>334</v>
+        <v>372</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>335</v>
+        <v>373</v>
       </c>
       <c r="I83" s="2">
         <v>1</v>
@@ -4155,28 +4152,28 @@
     </row>
     <row r="84" spans="1:9" ht="102.5" x14ac:dyDescent="0.45">
       <c r="A84" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>336</v>
+        <v>374</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>337</v>
+        <v>375</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>338</v>
+        <v>376</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>339</v>
+        <v>377</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>340</v>
+        <v>378</v>
       </c>
       <c r="I84" s="2">
         <v>3</v>
@@ -4184,28 +4181,28 @@
     </row>
     <row r="85" spans="1:9" ht="102.5" x14ac:dyDescent="0.45">
       <c r="A85" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>341</v>
+        <v>379</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>342</v>
+        <v>380</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>343</v>
+        <v>381</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>344</v>
+        <v>382</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>153</v>
+        <v>177</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>345</v>
+        <v>383</v>
       </c>
       <c r="I85" s="2">
         <v>1</v>
@@ -4213,115 +4210,115 @@
     </row>
     <row r="86" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A86" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>346</v>
+        <v>384</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>420</v>
+        <v>79</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>347</v>
+        <v>385</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>348</v>
+        <v>386</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A87" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>349</v>
+        <v>387</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>350</v>
+        <v>388</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>351</v>
+        <v>389</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>352</v>
+        <v>390</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>353</v>
+        <v>391</v>
       </c>
       <c r="I87" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A88" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>354</v>
+        <v>392</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>421</v>
+        <v>393</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>355</v>
+        <v>394</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>356</v>
+        <v>395</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="102.5" x14ac:dyDescent="0.45">
       <c r="A89" s="3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>357</v>
+        <v>396</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>422</v>
+        <v>397</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>358</v>
+        <v>398</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>359</v>
+        <v>399</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>356</v>
+        <v>395</v>
       </c>
       <c r="I89" s="2">
         <v>1</v>
@@ -4329,28 +4326,28 @@
     </row>
     <row r="90" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A90" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>360</v>
+        <v>400</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>361</v>
+        <v>401</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>362</v>
+        <v>402</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>363</v>
+        <v>403</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>364</v>
+        <v>404</v>
       </c>
       <c r="I90" s="2">
         <v>1</v>
@@ -4358,86 +4355,86 @@
     </row>
     <row r="91" spans="1:9" ht="102.5" x14ac:dyDescent="0.45">
       <c r="A91" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>365</v>
+        <v>405</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>423</v>
+        <v>406</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>366</v>
+        <v>407</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>367</v>
+        <v>408</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>368</v>
+        <v>409</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="92" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A92" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>369</v>
+        <v>410</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>424</v>
+        <v>411</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>370</v>
+        <v>412</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>371</v>
+        <v>413</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="93" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A93" s="3" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>372</v>
+        <v>414</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>373</v>
+        <v>416</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>374</v>
+        <v>417</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>375</v>
+        <v>418</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>371</v>
+        <v>413</v>
       </c>
       <c r="I93" s="2">
         <v>5</v>
@@ -4445,57 +4442,57 @@
     </row>
     <row r="94" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A94" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>376</v>
+        <v>419</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>426</v>
+        <v>48</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>377</v>
+        <v>420</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="95" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A95" s="3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B95" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G95" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="C95" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D95" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="E95" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="F95" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G95" s="4" t="s">
-        <v>51</v>
-      </c>
       <c r="H95" s="3" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="I95" s="2">
         <v>1</v>
@@ -4503,57 +4500,57 @@
     </row>
     <row r="96" spans="1:9" ht="102.5" x14ac:dyDescent="0.45">
       <c r="A96" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>380</v>
+        <v>423</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>427</v>
+        <v>76</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>381</v>
+        <v>424</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="I96" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="97" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A97" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>420</v>
+        <v>79</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>382</v>
+        <v>425</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>383</v>
+        <v>426</v>
       </c>
       <c r="F97" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="I97" s="2">
         <v>4</v>
